--- a/data/数据源8.10-8.14.xlsx
+++ b/data/数据源8.10-8.14.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'优沃森需求明细&amp;岗位JD'!$A$1:$Y$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'待入职表-优沃森'!$A$1:$P$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1761" uniqueCount="328">
   <si>
     <t>岗位</t>
   </si>
@@ -768,9 +769,6 @@
   </si>
   <si>
     <t>2-4w</t>
-  </si>
-  <si>
-    <t>朱秋深待复试</t>
   </si>
   <si>
     <t>活动运营经理</t>
@@ -2375,7 +2373,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:Y51"/>
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="16.8"/>
   <cols>
@@ -2466,7 +2464,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="2" ht="25.5" customHeight="1" spans="1:25">
       <c r="A2" t="s">
         <v>25</v>
       </c>
@@ -2537,7 +2535,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="3" ht="25.5" customHeight="1" spans="1:25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -2602,7 +2600,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="4" ht="25.5" customHeight="1" spans="1:25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -2670,7 +2668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="5" ht="25.5" customHeight="1" spans="1:25">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -2736,7 +2734,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="6" ht="25.5" customHeight="1" spans="1:25">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -2802,7 +2800,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="7" ht="25.5" customHeight="1" spans="1:25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -2868,7 +2866,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="8" ht="25.5" customHeight="1" spans="1:25">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -2936,7 +2934,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="9" ht="25.5" customHeight="1" spans="1:25">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -3004,7 +3002,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="10" ht="25.5" customHeight="1" spans="1:25">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -3072,7 +3070,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="11" ht="25.5" customHeight="1" spans="1:25">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -3140,7 +3138,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="12" ht="25.5" customHeight="1" spans="1:25">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -3208,7 +3206,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="13" ht="25.5" customHeight="1" spans="1:25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -3276,7 +3274,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="14" ht="25.5" customHeight="1" spans="1:25">
       <c r="A14" t="s">
         <v>77</v>
       </c>
@@ -3341,7 +3339,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="15" ht="25.5" customHeight="1" spans="1:25">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -3398,7 +3396,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" ht="25.5" hidden="1" customHeight="1" spans="1:25">
+    <row r="16" ht="25.5" customHeight="1" spans="1:25">
       <c r="A16" t="s">
         <v>84</v>
       </c>
@@ -3460,7 +3458,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="17" ht="25.5" customHeight="1" spans="1:23">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -3528,7 +3526,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="18" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="18" ht="25.5" customHeight="1" spans="1:23">
       <c r="A18" t="s">
         <v>94</v>
       </c>
@@ -3590,7 +3588,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="19" ht="25.5" customHeight="1" spans="1:23">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -3658,7 +3656,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="20" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="20" ht="25.5" customHeight="1" spans="1:23">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -3717,7 +3715,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="21" ht="25.5" customHeight="1" spans="1:23">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -3774,7 +3772,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="22" ht="25.5" customHeight="1" spans="1:23">
       <c r="A22" t="s">
         <v>103</v>
       </c>
@@ -3833,7 +3831,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="23" ht="25.5" customHeight="1" spans="1:23">
       <c r="A23" t="s">
         <v>105</v>
       </c>
@@ -3898,7 +3896,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="24" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="24" ht="25.5" customHeight="1" spans="1:23">
       <c r="A24" t="s">
         <v>110</v>
       </c>
@@ -3966,7 +3964,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="25" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="25" ht="25.5" customHeight="1" spans="1:23">
       <c r="A25" t="s">
         <v>114</v>
       </c>
@@ -4028,7 +4026,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="26" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="26" ht="25.5" customHeight="1" spans="1:23">
       <c r="A26" t="s">
         <v>118</v>
       </c>
@@ -4093,7 +4091,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="27" ht="25.5" customHeight="1" spans="1:23">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -4153,7 +4151,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="28" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="28" ht="25.5" customHeight="1" spans="1:23">
       <c r="A28" t="s">
         <v>128</v>
       </c>
@@ -4216,7 +4214,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="29" ht="25.5" customHeight="1" spans="1:23">
       <c r="A29" t="s">
         <v>132</v>
       </c>
@@ -4281,7 +4279,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="30" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="30" ht="25.5" customHeight="1" spans="1:23">
       <c r="A30" t="s">
         <v>136</v>
       </c>
@@ -4349,7 +4347,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="31" ht="25.5" customHeight="1" spans="1:23">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -4409,7 +4407,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="32" ht="25.5" hidden="1" customHeight="1" spans="1:23">
+    <row r="32" ht="25.5" customHeight="1" spans="1:23">
       <c r="A32" t="s">
         <v>140</v>
       </c>
@@ -4477,7 +4475,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" ht="25.5" hidden="1" customHeight="1" spans="1:22">
+    <row r="33" ht="25.5" customHeight="1" spans="1:22">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -4659,7 +4657,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" ht="25.5" hidden="1" customHeight="1" spans="1:22">
+    <row r="36" ht="25.5" customHeight="1" spans="1:22">
       <c r="A36" t="s">
         <v>153</v>
       </c>
@@ -4838,19 +4836,16 @@
       <c r="U38" t="s">
         <v>117</v>
       </c>
-      <c r="V38" t="s">
-        <v>161</v>
-      </c>
     </row>
     <row r="39" ht="25.5" customHeight="1" spans="1:22">
       <c r="A39" t="s">
+        <v>161</v>
+      </c>
+      <c r="B39" t="s">
         <v>162</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>163</v>
-      </c>
-      <c r="C39" t="s">
-        <v>164</v>
       </c>
       <c r="D39" t="s">
         <v>86</v>
@@ -4862,7 +4857,7 @@
         <v>30</v>
       </c>
       <c r="G39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I39" t="s">
         <v>32</v>
@@ -4901,13 +4896,13 @@
     </row>
     <row r="40" ht="25.5" customHeight="1" spans="1:22">
       <c r="A40" t="s">
+        <v>165</v>
+      </c>
+      <c r="B40" t="s">
         <v>166</v>
       </c>
-      <c r="B40" t="s">
-        <v>167</v>
-      </c>
       <c r="C40" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D40" t="s">
         <v>86</v>
@@ -4919,7 +4914,7 @@
         <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I40" t="s">
         <v>32</v>
@@ -4958,13 +4953,13 @@
     </row>
     <row r="41" ht="25.5" customHeight="1" spans="1:22">
       <c r="A41" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" t="s">
         <v>168</v>
       </c>
-      <c r="B41" t="s">
-        <v>169</v>
-      </c>
       <c r="C41" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D41" t="s">
         <v>86</v>
@@ -4976,7 +4971,7 @@
         <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I41" t="s">
         <v>121</v>
@@ -5015,13 +5010,13 @@
     </row>
     <row r="42" ht="25.5" customHeight="1" spans="1:22">
       <c r="A42" t="s">
+        <v>170</v>
+      </c>
+      <c r="B42" t="s">
         <v>171</v>
       </c>
-      <c r="B42" t="s">
-        <v>172</v>
-      </c>
       <c r="C42" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D42" t="s">
         <v>86</v>
@@ -5033,7 +5028,7 @@
         <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I42" t="s">
         <v>121</v>
@@ -5072,13 +5067,13 @@
     </row>
     <row r="43" ht="25.5" customHeight="1" spans="1:22">
       <c r="A43" t="s">
+        <v>172</v>
+      </c>
+      <c r="B43" t="s">
         <v>173</v>
       </c>
-      <c r="B43" t="s">
-        <v>174</v>
-      </c>
       <c r="C43" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D43" t="s">
         <v>86</v>
@@ -5126,10 +5121,10 @@
     </row>
     <row r="44" ht="25.5" customHeight="1" spans="1:22">
       <c r="A44" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" t="s">
         <v>171</v>
-      </c>
-      <c r="B44" t="s">
-        <v>172</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
@@ -5144,7 +5139,7 @@
         <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I44" t="s">
         <v>121</v>
@@ -5183,10 +5178,10 @@
     </row>
     <row r="45" ht="25.5" customHeight="1" spans="1:22">
       <c r="A45" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" t="s">
         <v>175</v>
-      </c>
-      <c r="B45" t="s">
-        <v>176</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
@@ -5201,7 +5196,7 @@
         <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I45" t="s">
         <v>32</v>
@@ -5240,10 +5235,10 @@
     </row>
     <row r="46" ht="25.5" customHeight="1" spans="1:22">
       <c r="A46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B46" t="s">
         <v>177</v>
-      </c>
-      <c r="B46" t="s">
-        <v>178</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
@@ -5258,7 +5253,7 @@
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I46" t="s">
         <v>32</v>
@@ -5297,10 +5292,10 @@
     </row>
     <row r="47" ht="25.5" customHeight="1" spans="1:22">
       <c r="A47" t="s">
+        <v>179</v>
+      </c>
+      <c r="B47" t="s">
         <v>180</v>
-      </c>
-      <c r="B47" t="s">
-        <v>181</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
@@ -5318,7 +5313,7 @@
         <v>130</v>
       </c>
       <c r="I47" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -5354,7 +5349,7 @@
     </row>
     <row r="48" ht="25.5" customHeight="1" spans="1:22">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B48" t="s">
         <v>125</v>
@@ -5366,7 +5361,7 @@
         <v>79</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
@@ -5414,7 +5409,7 @@
     </row>
     <row r="49" ht="25.5" customHeight="1" spans="1:20">
       <c r="A49" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
         <v>129</v>
@@ -5471,10 +5466,10 @@
     </row>
     <row r="50" ht="25.5" customHeight="1" spans="1:20">
       <c r="A50" t="s">
+        <v>185</v>
+      </c>
+      <c r="B50" t="s">
         <v>186</v>
-      </c>
-      <c r="B50" t="s">
-        <v>187</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -5525,7 +5520,7 @@
     </row>
     <row r="51" ht="25.5" customHeight="1" spans="1:20">
       <c r="A51" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -5540,7 +5535,7 @@
         <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I51" t="s">
         <v>48</v>
@@ -5579,11 +5574,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:Y51" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="19">
-      <filters>
-        <filter val="招聘进行中"/>
-      </filters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <dataValidations count="5">
@@ -5619,52 +5609,52 @@
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" spans="1:16">
@@ -5675,46 +5665,46 @@
         <v>91</v>
       </c>
       <c r="C2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" t="s">
         <v>205</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>206</v>
-      </c>
-      <c r="E2" t="s">
-        <v>207</v>
       </c>
       <c r="F2" t="s">
         <v>46</v>
       </c>
       <c r="G2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I2" s="2">
         <v>46251</v>
       </c>
       <c r="J2" t="s">
+        <v>208</v>
+      </c>
+      <c r="K2" t="s">
         <v>209</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M2" t="s">
         <v>210</v>
       </c>
-      <c r="L2" t="s">
-        <v>210</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>211</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>212</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>213</v>
-      </c>
-      <c r="P2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:16">
@@ -5725,13 +5715,13 @@
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F3" t="s">
         <v>29</v>
@@ -5746,7 +5736,7 @@
         <v>46156</v>
       </c>
       <c r="J3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K3" t="s">
         <v>41</v>
@@ -5755,13 +5745,13 @@
         <v>41</v>
       </c>
       <c r="M3" t="s">
+        <v>215</v>
+      </c>
+      <c r="N3" t="s">
         <v>216</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>217</v>
-      </c>
-      <c r="O3" t="s">
-        <v>218</v>
       </c>
       <c r="P3" t="s">
         <v>35</v>
@@ -5775,13 +5765,13 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F4" t="s">
         <v>46</v>
@@ -5796,7 +5786,7 @@
         <v>46160</v>
       </c>
       <c r="J4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K4" t="s">
         <v>79</v>
@@ -5805,13 +5795,13 @@
         <v>79</v>
       </c>
       <c r="M4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P4" t="s">
         <v>35</v>
@@ -5825,13 +5815,13 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -5840,13 +5830,13 @@
         <v>27</v>
       </c>
       <c r="H5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I5" s="2">
         <v>46167</v>
       </c>
       <c r="J5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K5" t="s">
         <v>50</v>
@@ -5855,13 +5845,13 @@
         <v>50</v>
       </c>
       <c r="M5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P5" t="s">
         <v>35</v>
@@ -5875,13 +5865,13 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F6" t="s">
         <v>46</v>
@@ -5890,13 +5880,13 @@
         <v>27</v>
       </c>
       <c r="H6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I6" s="2">
         <v>46168</v>
       </c>
       <c r="J6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K6" t="s">
         <v>50</v>
@@ -5905,13 +5895,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P6" t="s">
         <v>35</v>
@@ -5925,13 +5915,13 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F7" t="s">
         <v>59</v>
@@ -5940,13 +5930,13 @@
         <v>27</v>
       </c>
       <c r="H7" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I7" s="2">
         <v>46174</v>
       </c>
       <c r="J7" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K7" t="s">
         <v>50</v>
@@ -5955,13 +5945,13 @@
         <v>50</v>
       </c>
       <c r="M7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P7" t="s">
         <v>35</v>
@@ -5975,13 +5965,13 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -5990,13 +5980,13 @@
         <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I8" s="2">
         <v>46167</v>
       </c>
       <c r="J8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K8" t="s">
         <v>28</v>
@@ -6005,13 +5995,13 @@
         <v>28</v>
       </c>
       <c r="M8" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N8" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P8" t="s">
         <v>35</v>
@@ -6025,13 +6015,13 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F9" t="s">
         <v>46</v>
@@ -6040,13 +6030,13 @@
         <v>27</v>
       </c>
       <c r="H9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I9" s="2">
         <v>46161</v>
       </c>
       <c r="J9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K9" t="s">
         <v>79</v>
@@ -6055,13 +6045,13 @@
         <v>79</v>
       </c>
       <c r="M9" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P9" t="s">
         <v>35</v>
@@ -6075,13 +6065,13 @@
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F10" t="s">
         <v>46</v>
@@ -6096,7 +6086,7 @@
         <v>46161</v>
       </c>
       <c r="J10" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K10" t="s">
         <v>79</v>
@@ -6105,13 +6095,13 @@
         <v>79</v>
       </c>
       <c r="M10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P10" t="s">
         <v>35</v>
@@ -6125,13 +6115,13 @@
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F11" t="s">
         <v>46</v>
@@ -6140,13 +6130,13 @@
         <v>27</v>
       </c>
       <c r="H11" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I11" s="2">
         <v>46167</v>
       </c>
       <c r="J11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K11" t="s">
         <v>86</v>
@@ -6155,13 +6145,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N11" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P11" t="s">
         <v>35</v>
@@ -6175,13 +6165,13 @@
         <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E12" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F12" t="s">
         <v>46</v>
@@ -6196,7 +6186,7 @@
         <v>46170</v>
       </c>
       <c r="J12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K12" t="s">
         <v>79</v>
@@ -6205,13 +6195,13 @@
         <v>79</v>
       </c>
       <c r="M12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P12" t="s">
         <v>35</v>
@@ -6225,13 +6215,13 @@
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F13" t="s">
         <v>46</v>
@@ -6240,13 +6230,13 @@
         <v>27</v>
       </c>
       <c r="H13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I13" s="2">
         <v>46164</v>
       </c>
       <c r="J13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K13" t="s">
         <v>86</v>
@@ -6255,13 +6245,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N13" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P13" t="s">
         <v>35</v>
@@ -6275,13 +6265,13 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D14" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F14" t="s">
         <v>46</v>
@@ -6290,13 +6280,13 @@
         <v>27</v>
       </c>
       <c r="H14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I14" s="2">
         <v>46181</v>
       </c>
       <c r="J14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K14" t="s">
         <v>50</v>
@@ -6305,13 +6295,13 @@
         <v>50</v>
       </c>
       <c r="M14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P14" t="s">
         <v>35</v>
@@ -6325,13 +6315,13 @@
         <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F15" t="s">
         <v>46</v>
@@ -6340,13 +6330,13 @@
         <v>27</v>
       </c>
       <c r="H15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I15" s="2">
         <v>46174</v>
       </c>
       <c r="J15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K15" t="s">
         <v>86</v>
@@ -6355,16 +6345,16 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N15" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O15" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" ht="25.5" customHeight="1" spans="1:16">
@@ -6375,13 +6365,13 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D16" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F16" t="s">
         <v>46</v>
@@ -6390,13 +6380,13 @@
         <v>27</v>
       </c>
       <c r="H16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I16" s="2">
         <v>46174</v>
       </c>
       <c r="J16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K16" t="s">
         <v>86</v>
@@ -6405,16 +6395,16 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P16" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" ht="25.5" customHeight="1" spans="1:16">
@@ -6425,13 +6415,13 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
@@ -6440,13 +6430,13 @@
         <v>27</v>
       </c>
       <c r="H17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I17" s="2">
         <v>46181</v>
       </c>
       <c r="J17" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K17" t="s">
         <v>50</v>
@@ -6455,13 +6445,13 @@
         <v>50</v>
       </c>
       <c r="M17" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O17" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P17" t="s">
         <v>35</v>
@@ -6475,13 +6465,13 @@
         <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F18" t="s">
         <v>29</v>
@@ -6490,13 +6480,13 @@
         <v>27</v>
       </c>
       <c r="H18" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I18" s="2">
         <v>46188</v>
       </c>
       <c r="J18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K18" t="s">
         <v>50</v>
@@ -6505,16 +6495,16 @@
         <v>50</v>
       </c>
       <c r="M18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N18" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O18" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P18" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" ht="25.5" customHeight="1" spans="1:16">
@@ -6525,13 +6515,13 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F19" t="s">
         <v>29</v>
@@ -6540,13 +6530,13 @@
         <v>27</v>
       </c>
       <c r="H19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I19" s="2">
         <v>46188</v>
       </c>
       <c r="J19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K19" t="s">
         <v>50</v>
@@ -6555,13 +6545,13 @@
         <v>50</v>
       </c>
       <c r="M19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P19" t="s">
         <v>35</v>
@@ -6575,13 +6565,13 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D20" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E20" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
@@ -6590,13 +6580,13 @@
         <v>27</v>
       </c>
       <c r="H20" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I20" s="2">
         <v>46188</v>
       </c>
       <c r="J20" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K20" t="s">
         <v>50</v>
@@ -6605,16 +6595,16 @@
         <v>50</v>
       </c>
       <c r="M20" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O20" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" ht="25.5" customHeight="1" spans="1:16">
@@ -6625,13 +6615,13 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F21" t="s">
         <v>29</v>
@@ -6640,13 +6630,13 @@
         <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I21" s="2">
         <v>46188</v>
       </c>
       <c r="J21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K21" t="s">
         <v>50</v>
@@ -6655,13 +6645,13 @@
         <v>50</v>
       </c>
       <c r="M21" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O21" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s">
         <v>35</v>
@@ -6675,13 +6665,13 @@
         <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
@@ -6690,13 +6680,13 @@
         <v>27</v>
       </c>
       <c r="H22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I22" s="2">
         <v>46196</v>
       </c>
       <c r="J22" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K22" t="s">
         <v>93</v>
@@ -6705,13 +6695,13 @@
         <v>93</v>
       </c>
       <c r="M22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P22" t="s">
         <v>35</v>
@@ -6725,13 +6715,13 @@
         <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
@@ -6740,13 +6730,13 @@
         <v>27</v>
       </c>
       <c r="H23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I23" s="2">
         <v>46198</v>
       </c>
       <c r="J23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K23" t="s">
         <v>93</v>
@@ -6755,13 +6745,13 @@
         <v>93</v>
       </c>
       <c r="M23" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N23" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O23" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P23" t="s">
         <v>35</v>
@@ -6775,13 +6765,13 @@
         <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
@@ -6790,13 +6780,13 @@
         <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I24" s="2">
         <v>46199</v>
       </c>
       <c r="J24" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K24" t="s">
         <v>93</v>
@@ -6805,13 +6795,13 @@
         <v>93</v>
       </c>
       <c r="M24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P24" t="s">
         <v>35</v>
@@ -6825,13 +6815,13 @@
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D25" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E25" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
@@ -6840,13 +6830,13 @@
         <v>27</v>
       </c>
       <c r="H25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I25" s="2">
         <v>46195</v>
       </c>
       <c r="J25" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K25" t="s">
         <v>50</v>
@@ -6855,13 +6845,13 @@
         <v>50</v>
       </c>
       <c r="M25" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N25" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P25" t="s">
         <v>35</v>
@@ -6875,40 +6865,40 @@
         <v>116</v>
       </c>
       <c r="C26" t="s">
+        <v>247</v>
+      </c>
+      <c r="D26" t="s">
         <v>248</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>249</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>250</v>
       </c>
-      <c r="F26" t="s">
+      <c r="G26" t="s">
+        <v>27</v>
+      </c>
+      <c r="H26" t="s">
         <v>251</v>
-      </c>
-      <c r="G26" t="s">
-        <v>27</v>
-      </c>
-      <c r="H26" t="s">
-        <v>252</v>
       </c>
       <c r="I26" s="2">
         <v>46209</v>
       </c>
       <c r="J26" t="s">
+        <v>252</v>
+      </c>
+      <c r="K26" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" t="s">
+        <v>79</v>
+      </c>
+      <c r="M26" t="s">
         <v>253</v>
       </c>
-      <c r="K26" t="s">
-        <v>79</v>
-      </c>
-      <c r="L26" t="s">
-        <v>79</v>
-      </c>
-      <c r="M26" t="s">
-        <v>254</v>
-      </c>
       <c r="N26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O26" t="s">
         <v>127</v>
@@ -6925,13 +6915,13 @@
         <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D27" t="s">
+        <v>254</v>
+      </c>
+      <c r="E27" t="s">
         <v>255</v>
-      </c>
-      <c r="E27" t="s">
-        <v>256</v>
       </c>
       <c r="F27" t="s">
         <v>29</v>
@@ -6940,13 +6930,13 @@
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I27" s="2">
         <v>46204</v>
       </c>
       <c r="J27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K27" t="s">
         <v>79</v>
@@ -6955,13 +6945,13 @@
         <v>79</v>
       </c>
       <c r="M27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P27" t="s">
         <v>35</v>
@@ -6975,13 +6965,13 @@
         <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D28" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E28" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F28" t="s">
         <v>29</v>
@@ -6996,7 +6986,7 @@
         <v>46204</v>
       </c>
       <c r="J28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K28" t="s">
         <v>79</v>
@@ -7005,13 +6995,13 @@
         <v>79</v>
       </c>
       <c r="M28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N28" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O28" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P28" t="s">
         <v>35</v>
@@ -7025,46 +7015,46 @@
         <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D29" t="s">
+        <v>258</v>
+      </c>
+      <c r="E29" t="s">
+        <v>249</v>
+      </c>
+      <c r="F29" t="s">
         <v>259</v>
       </c>
-      <c r="E29" t="s">
-        <v>250</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="G29" t="s">
+        <v>27</v>
+      </c>
+      <c r="H29" t="s">
         <v>260</v>
-      </c>
-      <c r="G29" t="s">
-        <v>27</v>
-      </c>
-      <c r="H29" t="s">
-        <v>261</v>
       </c>
       <c r="I29" s="2">
         <v>46209</v>
       </c>
       <c r="J29" t="s">
+        <v>252</v>
+      </c>
+      <c r="K29" t="s">
+        <v>79</v>
+      </c>
+      <c r="L29" t="s">
+        <v>79</v>
+      </c>
+      <c r="M29" t="s">
         <v>253</v>
       </c>
-      <c r="K29" t="s">
-        <v>79</v>
-      </c>
-      <c r="L29" t="s">
-        <v>79</v>
-      </c>
-      <c r="M29" t="s">
-        <v>254</v>
-      </c>
       <c r="N29" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O29" t="s">
         <v>127</v>
       </c>
       <c r="P29" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="30" ht="25.5" customHeight="1" spans="1:16">
@@ -7075,46 +7065,46 @@
         <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D30" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E30" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F30" t="s">
+        <v>259</v>
+      </c>
+      <c r="G30" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" t="s">
         <v>260</v>
-      </c>
-      <c r="G30" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" t="s">
-        <v>261</v>
       </c>
       <c r="I30" s="2">
         <v>46209</v>
       </c>
       <c r="J30" t="s">
+        <v>252</v>
+      </c>
+      <c r="K30" t="s">
+        <v>79</v>
+      </c>
+      <c r="L30" t="s">
+        <v>79</v>
+      </c>
+      <c r="M30" t="s">
         <v>253</v>
       </c>
-      <c r="K30" t="s">
-        <v>79</v>
-      </c>
-      <c r="L30" t="s">
-        <v>79</v>
-      </c>
-      <c r="M30" t="s">
-        <v>254</v>
-      </c>
       <c r="N30" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O30" t="s">
         <v>127</v>
       </c>
       <c r="P30" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="31" ht="25.5" customHeight="1" spans="1:16">
@@ -7125,46 +7115,46 @@
         <v>91</v>
       </c>
       <c r="C31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D31" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E31" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" t="s">
         <v>250</v>
       </c>
-      <c r="F31" t="s">
-        <v>251</v>
-      </c>
       <c r="G31" t="s">
         <v>27</v>
       </c>
       <c r="H31" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I31" s="2">
         <v>46215</v>
       </c>
       <c r="J31" t="s">
+        <v>252</v>
+      </c>
+      <c r="K31" t="s">
+        <v>79</v>
+      </c>
+      <c r="L31" t="s">
+        <v>79</v>
+      </c>
+      <c r="M31" t="s">
         <v>253</v>
       </c>
-      <c r="K31" t="s">
-        <v>79</v>
-      </c>
-      <c r="L31" t="s">
-        <v>79</v>
-      </c>
-      <c r="M31" t="s">
-        <v>254</v>
-      </c>
       <c r="N31" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O31" t="s">
         <v>127</v>
       </c>
       <c r="P31" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" ht="25.5" customHeight="1" spans="1:16">
@@ -7175,40 +7165,40 @@
         <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D32" t="s">
+        <v>263</v>
+      </c>
+      <c r="E32" t="s">
+        <v>249</v>
+      </c>
+      <c r="F32" t="s">
         <v>264</v>
       </c>
-      <c r="E32" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" t="s">
-        <v>265</v>
-      </c>
       <c r="G32" t="s">
         <v>27</v>
       </c>
       <c r="H32" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I32" s="2">
         <v>46209</v>
       </c>
       <c r="J32" t="s">
+        <v>252</v>
+      </c>
+      <c r="K32" t="s">
+        <v>79</v>
+      </c>
+      <c r="L32" t="s">
+        <v>79</v>
+      </c>
+      <c r="M32" t="s">
         <v>253</v>
       </c>
-      <c r="K32" t="s">
-        <v>79</v>
-      </c>
-      <c r="L32" t="s">
-        <v>79</v>
-      </c>
-      <c r="M32" t="s">
-        <v>254</v>
-      </c>
       <c r="N32" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O32" t="s">
         <v>127</v>
@@ -7225,40 +7215,40 @@
         <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D33" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F33" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G33" t="s">
         <v>27</v>
       </c>
       <c r="H33" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I33" s="2">
         <v>46209</v>
       </c>
       <c r="J33" t="s">
+        <v>252</v>
+      </c>
+      <c r="K33" t="s">
+        <v>79</v>
+      </c>
+      <c r="L33" t="s">
+        <v>79</v>
+      </c>
+      <c r="M33" t="s">
         <v>253</v>
       </c>
-      <c r="K33" t="s">
-        <v>79</v>
-      </c>
-      <c r="L33" t="s">
-        <v>79</v>
-      </c>
-      <c r="M33" t="s">
-        <v>254</v>
-      </c>
       <c r="N33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O33" t="s">
         <v>127</v>
@@ -7275,13 +7265,13 @@
         <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D34" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E34" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F34" t="s">
         <v>29</v>
@@ -7290,28 +7280,28 @@
         <v>27</v>
       </c>
       <c r="H34" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I34" s="2">
         <v>46209</v>
       </c>
       <c r="J34" t="s">
+        <v>208</v>
+      </c>
+      <c r="K34" t="s">
         <v>209</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" t="s">
+        <v>209</v>
+      </c>
+      <c r="M34" t="s">
         <v>210</v>
       </c>
-      <c r="L34" t="s">
-        <v>210</v>
-      </c>
-      <c r="M34" t="s">
-        <v>211</v>
-      </c>
       <c r="N34" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O34" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P34" t="s">
         <v>35</v>
@@ -7325,13 +7315,13 @@
         <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D35" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F35" t="s">
         <v>46</v>
@@ -7340,13 +7330,13 @@
         <v>27</v>
       </c>
       <c r="H35" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I35" s="2">
         <v>46204</v>
       </c>
       <c r="J35" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K35" t="s">
         <v>93</v>
@@ -7355,13 +7345,13 @@
         <v>93</v>
       </c>
       <c r="M35" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N35" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P35" t="s">
         <v>35</v>
@@ -7375,40 +7365,40 @@
         <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E36" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F36" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G36" t="s">
         <v>27</v>
       </c>
       <c r="H36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I36" s="2">
         <v>46209</v>
       </c>
       <c r="J36" t="s">
+        <v>252</v>
+      </c>
+      <c r="K36" t="s">
+        <v>79</v>
+      </c>
+      <c r="L36" t="s">
+        <v>79</v>
+      </c>
+      <c r="M36" t="s">
         <v>253</v>
       </c>
-      <c r="K36" t="s">
-        <v>79</v>
-      </c>
-      <c r="L36" t="s">
-        <v>79</v>
-      </c>
-      <c r="M36" t="s">
-        <v>254</v>
-      </c>
       <c r="N36" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O36" t="s">
         <v>127</v>
@@ -7425,13 +7415,13 @@
         <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F37" t="s">
         <v>46</v>
@@ -7440,13 +7430,13 @@
         <v>27</v>
       </c>
       <c r="H37" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I37" s="2">
         <v>46209</v>
       </c>
       <c r="J37" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K37" t="s">
         <v>93</v>
@@ -7455,13 +7445,13 @@
         <v>93</v>
       </c>
       <c r="M37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N37" t="s">
+        <v>216</v>
+      </c>
+      <c r="O37" t="s">
         <v>217</v>
-      </c>
-      <c r="O37" t="s">
-        <v>218</v>
       </c>
       <c r="P37" t="s">
         <v>35</v>
@@ -7475,13 +7465,13 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E38" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F38" t="s">
         <v>46</v>
@@ -7490,13 +7480,13 @@
         <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I38" s="2">
         <v>46224</v>
       </c>
       <c r="J38" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K38" t="s">
         <v>79</v>
@@ -7505,13 +7495,13 @@
         <v>79</v>
       </c>
       <c r="M38" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N38" t="s">
+        <v>216</v>
+      </c>
+      <c r="O38" t="s">
         <v>217</v>
-      </c>
-      <c r="O38" t="s">
-        <v>218</v>
       </c>
       <c r="P38" t="s">
         <v>35</v>
@@ -7525,13 +7515,13 @@
         <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D39" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F39" t="s">
         <v>29</v>
@@ -7540,13 +7530,13 @@
         <v>27</v>
       </c>
       <c r="H39" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I39" s="2">
         <v>46209</v>
       </c>
       <c r="J39" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K39" t="s">
         <v>79</v>
@@ -7555,13 +7545,13 @@
         <v>79</v>
       </c>
       <c r="M39" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N39" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O39" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P39" t="s">
         <v>35</v>
@@ -7575,13 +7565,13 @@
         <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E40" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F40" t="s">
         <v>29</v>
@@ -7590,13 +7580,13 @@
         <v>27</v>
       </c>
       <c r="H40" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I40" s="2">
         <v>46209</v>
       </c>
       <c r="J40" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K40" t="s">
         <v>79</v>
@@ -7605,13 +7595,13 @@
         <v>79</v>
       </c>
       <c r="M40" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N40" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P40" t="s">
         <v>35</v>
@@ -7625,13 +7615,13 @@
         <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D41" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F41" t="s">
         <v>29</v>
@@ -7646,7 +7636,7 @@
         <v>46209</v>
       </c>
       <c r="J41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K41" t="s">
         <v>79</v>
@@ -7655,13 +7645,13 @@
         <v>79</v>
       </c>
       <c r="M41" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N41" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O41" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P41" t="s">
         <v>35</v>
@@ -7675,13 +7665,13 @@
         <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E42" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F42" t="s">
         <v>46</v>
@@ -7690,13 +7680,13 @@
         <v>27</v>
       </c>
       <c r="H42" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I42" s="2">
         <v>46210</v>
       </c>
       <c r="J42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K42" t="s">
         <v>93</v>
@@ -7705,13 +7695,13 @@
         <v>93</v>
       </c>
       <c r="M42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N42" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O42" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P42" t="s">
         <v>35</v>
@@ -7725,13 +7715,13 @@
         <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D43" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F43" t="s">
         <v>46</v>
@@ -7740,13 +7730,13 @@
         <v>27</v>
       </c>
       <c r="H43" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I43" s="2">
         <v>46209</v>
       </c>
       <c r="J43" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K43" t="s">
         <v>93</v>
@@ -7755,16 +7745,16 @@
         <v>93</v>
       </c>
       <c r="M43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N43" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O43" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P43" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="44" ht="25.5" customHeight="1" spans="1:16">
@@ -7775,46 +7765,46 @@
         <v>33</v>
       </c>
       <c r="C44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D44" t="s">
+        <v>278</v>
+      </c>
+      <c r="E44" t="s">
+        <v>249</v>
+      </c>
+      <c r="F44" t="s">
         <v>279</v>
       </c>
-      <c r="E44" t="s">
-        <v>250</v>
-      </c>
-      <c r="F44" t="s">
-        <v>280</v>
-      </c>
       <c r="G44" t="s">
         <v>27</v>
       </c>
       <c r="H44" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I44" s="2">
         <v>46216</v>
       </c>
       <c r="J44" t="s">
+        <v>252</v>
+      </c>
+      <c r="K44" t="s">
+        <v>79</v>
+      </c>
+      <c r="L44" t="s">
+        <v>280</v>
+      </c>
+      <c r="M44" t="s">
         <v>253</v>
       </c>
-      <c r="K44" t="s">
-        <v>79</v>
-      </c>
-      <c r="L44" t="s">
-        <v>281</v>
-      </c>
-      <c r="M44" t="s">
-        <v>254</v>
-      </c>
       <c r="N44" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O44" t="s">
         <v>127</v>
       </c>
       <c r="P44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="45" ht="25.5" customHeight="1" spans="1:16">
@@ -7825,13 +7815,13 @@
         <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D45" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F45" t="s">
         <v>29</v>
@@ -7840,13 +7830,13 @@
         <v>27</v>
       </c>
       <c r="H45" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I45" s="2">
         <v>46210</v>
       </c>
       <c r="J45" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K45" t="s">
         <v>86</v>
@@ -7855,13 +7845,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N45" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O45" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P45" t="s">
         <v>35</v>
@@ -7875,13 +7865,13 @@
         <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D46" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E46" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F46" t="s">
         <v>29</v>
@@ -7890,13 +7880,13 @@
         <v>27</v>
       </c>
       <c r="H46" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I46" s="2">
         <v>46210</v>
       </c>
       <c r="J46" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K46" t="s">
         <v>86</v>
@@ -7905,13 +7895,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N46" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O46" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P46" t="s">
         <v>35</v>
@@ -7925,13 +7915,13 @@
         <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D47" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F47" t="s">
         <v>29</v>
@@ -7940,13 +7930,13 @@
         <v>27</v>
       </c>
       <c r="H47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I47" s="2">
         <v>46210</v>
       </c>
       <c r="J47" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K47" t="s">
         <v>86</v>
@@ -7955,13 +7945,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N47" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O47" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P47" t="s">
         <v>35</v>
@@ -7975,13 +7965,13 @@
         <v>134</v>
       </c>
       <c r="C48" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D48" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E48" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F48" t="s">
         <v>29</v>
@@ -7990,13 +7980,13 @@
         <v>27</v>
       </c>
       <c r="H48" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I48" s="2">
         <v>46210</v>
       </c>
       <c r="J48" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K48" t="s">
         <v>86</v>
@@ -8005,13 +7995,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N48" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O48" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P48" t="s">
         <v>35</v>
@@ -8025,40 +8015,40 @@
         <v>91</v>
       </c>
       <c r="C49" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D49" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E49" t="s">
+        <v>249</v>
+      </c>
+      <c r="F49" t="s">
         <v>250</v>
       </c>
-      <c r="F49" t="s">
-        <v>251</v>
-      </c>
       <c r="G49" t="s">
         <v>27</v>
       </c>
       <c r="H49" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I49" s="2">
         <v>46213</v>
       </c>
       <c r="J49" t="s">
+        <v>252</v>
+      </c>
+      <c r="K49" t="s">
+        <v>79</v>
+      </c>
+      <c r="L49" t="s">
+        <v>79</v>
+      </c>
+      <c r="M49" t="s">
         <v>253</v>
       </c>
-      <c r="K49" t="s">
-        <v>79</v>
-      </c>
-      <c r="L49" t="s">
-        <v>79</v>
-      </c>
-      <c r="M49" t="s">
-        <v>254</v>
-      </c>
       <c r="N49" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O49" t="s">
         <v>127</v>
@@ -8075,40 +8065,40 @@
         <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D50" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E50" t="s">
+        <v>249</v>
+      </c>
+      <c r="F50" t="s">
         <v>250</v>
       </c>
-      <c r="F50" t="s">
-        <v>251</v>
-      </c>
       <c r="G50" t="s">
         <v>27</v>
       </c>
       <c r="H50" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I50" s="2">
         <v>46213</v>
       </c>
       <c r="J50" t="s">
+        <v>252</v>
+      </c>
+      <c r="K50" t="s">
+        <v>79</v>
+      </c>
+      <c r="L50" t="s">
+        <v>79</v>
+      </c>
+      <c r="M50" t="s">
         <v>253</v>
       </c>
-      <c r="K50" t="s">
-        <v>79</v>
-      </c>
-      <c r="L50" t="s">
-        <v>79</v>
-      </c>
-      <c r="M50" t="s">
-        <v>254</v>
-      </c>
       <c r="N50" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O50" t="s">
         <v>127</v>
@@ -8125,44 +8115,44 @@
         <v>91</v>
       </c>
       <c r="C51" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D51" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E51" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F51" t="s">
+        <v>259</v>
+      </c>
+      <c r="G51" t="s">
+        <v>27</v>
+      </c>
+      <c r="H51" t="s">
         <v>260</v>
-      </c>
-      <c r="G51" t="s">
-        <v>27</v>
-      </c>
-      <c r="H51" t="s">
-        <v>261</v>
       </c>
       <c r="I51" s="2"/>
       <c r="J51" t="s">
+        <v>252</v>
+      </c>
+      <c r="K51" t="s">
+        <v>79</v>
+      </c>
+      <c r="L51" t="s">
+        <v>79</v>
+      </c>
+      <c r="M51" t="s">
         <v>253</v>
       </c>
-      <c r="K51" t="s">
-        <v>79</v>
-      </c>
-      <c r="L51" t="s">
-        <v>79</v>
-      </c>
-      <c r="M51" t="s">
-        <v>254</v>
-      </c>
       <c r="N51" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O51" t="s">
         <v>127</v>
       </c>
       <c r="P51" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" ht="25.5" customHeight="1" spans="1:16">
@@ -8173,38 +8163,38 @@
         <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D52" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E52" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F52" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G52" t="s">
         <v>27</v>
       </c>
       <c r="H52" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I52" s="2"/>
       <c r="J52" t="s">
+        <v>252</v>
+      </c>
+      <c r="K52" t="s">
+        <v>79</v>
+      </c>
+      <c r="L52" t="s">
+        <v>79</v>
+      </c>
+      <c r="M52" t="s">
         <v>253</v>
       </c>
-      <c r="K52" t="s">
-        <v>79</v>
-      </c>
-      <c r="L52" t="s">
-        <v>79</v>
-      </c>
-      <c r="M52" t="s">
-        <v>254</v>
-      </c>
       <c r="N52" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O52" t="s">
         <v>127</v>
@@ -8221,44 +8211,44 @@
         <v>91</v>
       </c>
       <c r="C53" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D53" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E53" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F53" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G53" t="s">
         <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I53" s="2"/>
       <c r="J53" t="s">
+        <v>252</v>
+      </c>
+      <c r="K53" t="s">
+        <v>79</v>
+      </c>
+      <c r="L53" t="s">
+        <v>79</v>
+      </c>
+      <c r="M53" t="s">
         <v>253</v>
       </c>
-      <c r="K53" t="s">
-        <v>79</v>
-      </c>
-      <c r="L53" t="s">
-        <v>79</v>
-      </c>
-      <c r="M53" t="s">
-        <v>254</v>
-      </c>
       <c r="N53" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O53" t="s">
         <v>127</v>
       </c>
       <c r="P53" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="54" ht="25.5" customHeight="1" spans="1:16">
@@ -8269,13 +8259,13 @@
         <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D54" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E54" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F54" t="s">
         <v>46</v>
@@ -8284,13 +8274,13 @@
         <v>27</v>
       </c>
       <c r="H54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I54" s="2">
         <v>46217</v>
       </c>
       <c r="J54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K54" t="s">
         <v>93</v>
@@ -8299,13 +8289,13 @@
         <v>93</v>
       </c>
       <c r="M54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O54" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P54" t="s">
         <v>35</v>
@@ -8319,13 +8309,13 @@
         <v>122</v>
       </c>
       <c r="C55" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D55" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E55" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F55" t="s">
         <v>46</v>
@@ -8334,13 +8324,13 @@
         <v>27</v>
       </c>
       <c r="H55" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I55" s="2">
         <v>46223</v>
       </c>
       <c r="J55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K55" t="s">
         <v>93</v>
@@ -8349,13 +8339,13 @@
         <v>93</v>
       </c>
       <c r="M55" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N55" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O55" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P55" t="s">
         <v>35</v>
@@ -8369,13 +8359,13 @@
         <v>122</v>
       </c>
       <c r="C56" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D56" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E56" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F56" t="s">
         <v>46</v>
@@ -8384,13 +8374,13 @@
         <v>27</v>
       </c>
       <c r="H56" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I56" s="2">
         <v>46217</v>
       </c>
       <c r="J56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K56" t="s">
         <v>93</v>
@@ -8399,13 +8389,13 @@
         <v>93</v>
       </c>
       <c r="M56" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O56" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P56" t="s">
         <v>35</v>
@@ -8419,13 +8409,13 @@
         <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D57" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E57" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F57" t="s">
         <v>46</v>
@@ -8434,13 +8424,13 @@
         <v>27</v>
       </c>
       <c r="H57" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I57" s="2">
         <v>46217</v>
       </c>
       <c r="J57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K57" t="s">
         <v>93</v>
@@ -8449,13 +8439,13 @@
         <v>93</v>
       </c>
       <c r="M57" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N57" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O57" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P57" t="s">
         <v>35</v>
@@ -8469,13 +8459,13 @@
         <v>122</v>
       </c>
       <c r="C58" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D58" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E58" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F58" t="s">
         <v>46</v>
@@ -8484,13 +8474,13 @@
         <v>27</v>
       </c>
       <c r="H58" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I58" s="2">
         <v>46217</v>
       </c>
       <c r="J58" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K58" t="s">
         <v>93</v>
@@ -8499,13 +8489,13 @@
         <v>93</v>
       </c>
       <c r="M58" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N58" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O58" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P58" t="s">
         <v>35</v>
@@ -8519,13 +8509,13 @@
         <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D59" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F59" t="s">
         <v>29</v>
@@ -8534,28 +8524,28 @@
         <v>27</v>
       </c>
       <c r="H59" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I59" s="2">
         <v>46216</v>
       </c>
       <c r="J59" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M59" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N59" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O59" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P59" t="s">
         <v>35</v>
@@ -8569,46 +8559,46 @@
         <v>91</v>
       </c>
       <c r="C60" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D60" t="s">
+        <v>299</v>
+      </c>
+      <c r="E60" t="s">
+        <v>249</v>
+      </c>
+      <c r="F60" t="s">
         <v>300</v>
       </c>
-      <c r="E60" t="s">
-        <v>250</v>
-      </c>
-      <c r="F60" t="s">
-        <v>301</v>
-      </c>
       <c r="G60" t="s">
         <v>27</v>
       </c>
       <c r="H60" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I60" s="2">
         <v>46219</v>
       </c>
       <c r="J60" t="s">
+        <v>252</v>
+      </c>
+      <c r="K60" t="s">
+        <v>79</v>
+      </c>
+      <c r="L60" t="s">
+        <v>79</v>
+      </c>
+      <c r="M60" t="s">
         <v>253</v>
       </c>
-      <c r="K60" t="s">
-        <v>79</v>
-      </c>
-      <c r="L60" t="s">
-        <v>79</v>
-      </c>
-      <c r="M60" t="s">
-        <v>254</v>
-      </c>
       <c r="N60" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O60" t="s">
         <v>127</v>
       </c>
       <c r="P60" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="61" ht="25.5" customHeight="1" spans="1:16">
@@ -8619,44 +8609,44 @@
         <v>116</v>
       </c>
       <c r="C61" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D61" t="s">
+        <v>301</v>
+      </c>
+      <c r="E61" t="s">
+        <v>249</v>
+      </c>
+      <c r="F61" t="s">
         <v>302</v>
       </c>
-      <c r="E61" t="s">
-        <v>250</v>
-      </c>
-      <c r="F61" t="s">
-        <v>303</v>
-      </c>
       <c r="G61" t="s">
         <v>27</v>
       </c>
       <c r="H61" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I61" s="2"/>
       <c r="J61" t="s">
+        <v>252</v>
+      </c>
+      <c r="K61" t="s">
+        <v>79</v>
+      </c>
+      <c r="L61" t="s">
+        <v>79</v>
+      </c>
+      <c r="M61" t="s">
         <v>253</v>
       </c>
-      <c r="K61" t="s">
-        <v>79</v>
-      </c>
-      <c r="L61" t="s">
-        <v>79</v>
-      </c>
-      <c r="M61" t="s">
-        <v>254</v>
-      </c>
       <c r="N61" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O61" t="s">
         <v>127</v>
       </c>
       <c r="P61" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="62" ht="25.5" customHeight="1" spans="1:16">
@@ -8667,46 +8657,46 @@
         <v>91</v>
       </c>
       <c r="C62" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D62" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E62" t="s">
+        <v>249</v>
+      </c>
+      <c r="F62" t="s">
         <v>250</v>
       </c>
-      <c r="F62" t="s">
-        <v>251</v>
-      </c>
       <c r="G62" t="s">
         <v>27</v>
       </c>
       <c r="H62" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I62" s="2">
         <v>46218</v>
       </c>
       <c r="J62" t="s">
+        <v>252</v>
+      </c>
+      <c r="K62" t="s">
+        <v>79</v>
+      </c>
+      <c r="L62" t="s">
+        <v>79</v>
+      </c>
+      <c r="M62" t="s">
         <v>253</v>
       </c>
-      <c r="K62" t="s">
-        <v>79</v>
-      </c>
-      <c r="L62" t="s">
-        <v>79</v>
-      </c>
-      <c r="M62" t="s">
-        <v>254</v>
-      </c>
       <c r="N62" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O62" t="s">
         <v>127</v>
       </c>
       <c r="P62" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="63" ht="25.5" customHeight="1" spans="1:16">
@@ -8717,13 +8707,13 @@
         <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D63" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E63" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F63" t="s">
         <v>46</v>
@@ -8732,13 +8722,13 @@
         <v>27</v>
       </c>
       <c r="H63" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I63" s="2">
         <v>46223</v>
       </c>
       <c r="J63" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K63" t="s">
         <v>93</v>
@@ -8747,13 +8737,13 @@
         <v>93</v>
       </c>
       <c r="M63" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N63" t="s">
+        <v>216</v>
+      </c>
+      <c r="O63" t="s">
         <v>217</v>
-      </c>
-      <c r="O63" t="s">
-        <v>218</v>
       </c>
       <c r="P63" t="s">
         <v>35</v>
@@ -8767,13 +8757,13 @@
         <v>122</v>
       </c>
       <c r="C64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D64" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F64" t="s">
         <v>46</v>
@@ -8782,13 +8772,13 @@
         <v>27</v>
       </c>
       <c r="H64" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I64" s="2">
         <v>46224</v>
       </c>
       <c r="J64" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K64" t="s">
         <v>93</v>
@@ -8797,13 +8787,13 @@
         <v>93</v>
       </c>
       <c r="M64" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N64" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="O64" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P64" t="s">
         <v>35</v>
@@ -8817,46 +8807,46 @@
         <v>91</v>
       </c>
       <c r="C65" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D65" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E65" t="s">
+        <v>249</v>
+      </c>
+      <c r="F65" t="s">
         <v>250</v>
       </c>
-      <c r="F65" t="s">
-        <v>251</v>
-      </c>
       <c r="G65" t="s">
         <v>27</v>
       </c>
       <c r="H65" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I65" s="2">
         <v>46223</v>
       </c>
       <c r="J65" t="s">
+        <v>252</v>
+      </c>
+      <c r="K65" t="s">
+        <v>79</v>
+      </c>
+      <c r="L65" t="s">
+        <v>79</v>
+      </c>
+      <c r="M65" t="s">
         <v>253</v>
       </c>
-      <c r="K65" t="s">
-        <v>79</v>
-      </c>
-      <c r="L65" t="s">
-        <v>79</v>
-      </c>
-      <c r="M65" t="s">
-        <v>254</v>
-      </c>
       <c r="N65" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O65" t="s">
         <v>127</v>
       </c>
       <c r="P65" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="66" ht="25.5" customHeight="1" spans="1:16">
@@ -8867,28 +8857,28 @@
         <v>33</v>
       </c>
       <c r="C66" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D66" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E66" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F66" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G66" t="s">
         <v>27</v>
       </c>
       <c r="H66" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I66" s="2">
         <v>46220</v>
       </c>
       <c r="J66" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K66" t="s">
         <v>79</v>
@@ -8897,10 +8887,10 @@
         <v>79</v>
       </c>
       <c r="M66" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N66" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O66" t="s">
         <v>127</v>
@@ -8917,28 +8907,28 @@
         <v>33</v>
       </c>
       <c r="C67" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D67" t="s">
+        <v>309</v>
+      </c>
+      <c r="E67" t="s">
+        <v>249</v>
+      </c>
+      <c r="F67" t="s">
         <v>310</v>
       </c>
-      <c r="E67" t="s">
-        <v>250</v>
-      </c>
-      <c r="F67" t="s">
-        <v>311</v>
-      </c>
       <c r="G67" t="s">
         <v>27</v>
       </c>
       <c r="H67" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I67" s="2">
         <v>46220</v>
       </c>
       <c r="J67" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K67" t="s">
         <v>79</v>
@@ -8947,10 +8937,10 @@
         <v>79</v>
       </c>
       <c r="M67" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N67" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O67" t="s">
         <v>127</v>
@@ -8967,28 +8957,28 @@
         <v>33</v>
       </c>
       <c r="C68" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D68" t="s">
+        <v>311</v>
+      </c>
+      <c r="E68" t="s">
+        <v>249</v>
+      </c>
+      <c r="F68" t="s">
         <v>312</v>
       </c>
-      <c r="E68" t="s">
-        <v>250</v>
-      </c>
-      <c r="F68" t="s">
-        <v>313</v>
-      </c>
       <c r="G68" t="s">
         <v>27</v>
       </c>
       <c r="H68" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I68" s="2">
         <v>46220</v>
       </c>
       <c r="J68" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K68" t="s">
         <v>79</v>
@@ -8997,10 +8987,10 @@
         <v>79</v>
       </c>
       <c r="M68" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N68" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O68" t="s">
         <v>127</v>
@@ -9017,40 +9007,40 @@
         <v>33</v>
       </c>
       <c r="C69" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D69" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E69" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F69" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G69" t="s">
         <v>27</v>
       </c>
       <c r="H69" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I69" s="2">
         <v>46221</v>
       </c>
       <c r="J69" t="s">
+        <v>252</v>
+      </c>
+      <c r="K69" t="s">
+        <v>79</v>
+      </c>
+      <c r="L69" t="s">
+        <v>79</v>
+      </c>
+      <c r="M69" t="s">
         <v>253</v>
       </c>
-      <c r="K69" t="s">
-        <v>79</v>
-      </c>
-      <c r="L69" t="s">
-        <v>79</v>
-      </c>
-      <c r="M69" t="s">
-        <v>254</v>
-      </c>
       <c r="N69" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O69" t="s">
         <v>127</v>
@@ -9067,40 +9057,40 @@
         <v>33</v>
       </c>
       <c r="C70" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D70" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E70" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F70" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G70" t="s">
         <v>27</v>
       </c>
       <c r="H70" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I70" s="2">
         <v>46221</v>
       </c>
       <c r="J70" t="s">
+        <v>252</v>
+      </c>
+      <c r="K70" t="s">
+        <v>79</v>
+      </c>
+      <c r="L70" t="s">
+        <v>79</v>
+      </c>
+      <c r="M70" t="s">
         <v>253</v>
       </c>
-      <c r="K70" t="s">
-        <v>79</v>
-      </c>
-      <c r="L70" t="s">
-        <v>79</v>
-      </c>
-      <c r="M70" t="s">
-        <v>254</v>
-      </c>
       <c r="N70" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O70" t="s">
         <v>127</v>
@@ -9117,40 +9107,40 @@
         <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D71" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E71" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F71" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G71" t="s">
         <v>27</v>
       </c>
       <c r="H71" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I71" s="2">
         <v>46220</v>
       </c>
       <c r="J71" t="s">
+        <v>252</v>
+      </c>
+      <c r="K71" t="s">
+        <v>79</v>
+      </c>
+      <c r="L71" t="s">
+        <v>79</v>
+      </c>
+      <c r="M71" t="s">
         <v>253</v>
       </c>
-      <c r="K71" t="s">
-        <v>79</v>
-      </c>
-      <c r="L71" t="s">
-        <v>79</v>
-      </c>
-      <c r="M71" t="s">
-        <v>254</v>
-      </c>
       <c r="N71" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O71" t="s">
         <v>127</v>
@@ -9167,13 +9157,13 @@
         <v>134</v>
       </c>
       <c r="C72" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D72" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E72" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F72" t="s">
         <v>29</v>
@@ -9182,13 +9172,13 @@
         <v>27</v>
       </c>
       <c r="H72" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I72" s="2">
         <v>46224</v>
       </c>
       <c r="J72" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K72" t="s">
         <v>86</v>
@@ -9197,13 +9187,13 @@
         <v>86</v>
       </c>
       <c r="M72" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N72" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O72" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P72" t="s">
         <v>35</v>
@@ -9217,13 +9207,13 @@
         <v>134</v>
       </c>
       <c r="C73" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D73" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E73" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F73" t="s">
         <v>29</v>
@@ -9232,13 +9222,13 @@
         <v>27</v>
       </c>
       <c r="H73" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I73" s="2">
         <v>46224</v>
       </c>
       <c r="J73" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K73" t="s">
         <v>86</v>
@@ -9247,13 +9237,13 @@
         <v>86</v>
       </c>
       <c r="M73" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N73" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O73" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="P73" t="s">
         <v>35</v>
@@ -9267,38 +9257,38 @@
         <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D74" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E74" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F74" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G74" t="s">
         <v>27</v>
       </c>
       <c r="H74" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I74" s="2"/>
       <c r="J74" t="s">
+        <v>252</v>
+      </c>
+      <c r="K74" t="s">
+        <v>79</v>
+      </c>
+      <c r="L74" t="s">
+        <v>79</v>
+      </c>
+      <c r="M74" t="s">
         <v>253</v>
       </c>
-      <c r="K74" t="s">
-        <v>79</v>
-      </c>
-      <c r="L74" t="s">
-        <v>79</v>
-      </c>
-      <c r="M74" t="s">
-        <v>254</v>
-      </c>
       <c r="N74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O74" t="s">
         <v>127</v>
@@ -9315,38 +9305,38 @@
         <v>91</v>
       </c>
       <c r="C75" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D75" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E75" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F75" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G75" t="s">
         <v>27</v>
       </c>
       <c r="H75" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I75" s="2"/>
       <c r="J75" t="s">
+        <v>252</v>
+      </c>
+      <c r="K75" t="s">
+        <v>79</v>
+      </c>
+      <c r="L75" t="s">
+        <v>79</v>
+      </c>
+      <c r="M75" t="s">
         <v>253</v>
       </c>
-      <c r="K75" t="s">
-        <v>79</v>
-      </c>
-      <c r="L75" t="s">
-        <v>79</v>
-      </c>
-      <c r="M75" t="s">
-        <v>254</v>
-      </c>
       <c r="N75" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O75" t="s">
         <v>127</v>
@@ -9363,40 +9353,40 @@
         <v>91</v>
       </c>
       <c r="C76" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D76" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E76" t="s">
+        <v>249</v>
+      </c>
+      <c r="F76" t="s">
         <v>250</v>
       </c>
-      <c r="F76" t="s">
-        <v>251</v>
-      </c>
       <c r="G76" t="s">
         <v>27</v>
       </c>
       <c r="H76" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I76" s="2">
         <v>46226</v>
       </c>
       <c r="J76" t="s">
+        <v>252</v>
+      </c>
+      <c r="K76" t="s">
+        <v>79</v>
+      </c>
+      <c r="L76" t="s">
+        <v>79</v>
+      </c>
+      <c r="M76" t="s">
         <v>253</v>
       </c>
-      <c r="K76" t="s">
-        <v>79</v>
-      </c>
-      <c r="L76" t="s">
-        <v>79</v>
-      </c>
-      <c r="M76" t="s">
-        <v>254</v>
-      </c>
       <c r="N76" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O76" t="s">
         <v>127</v>
@@ -9413,13 +9403,13 @@
         <v>122</v>
       </c>
       <c r="C77" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D77" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E77" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F77" t="s">
         <v>46</v>
@@ -9428,13 +9418,13 @@
         <v>27</v>
       </c>
       <c r="H77" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I77" s="2">
         <v>46232</v>
       </c>
       <c r="J77" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K77" t="s">
         <v>86</v>
@@ -9443,13 +9433,13 @@
         <v>86</v>
       </c>
       <c r="M77" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N77" t="s">
+        <v>216</v>
+      </c>
+      <c r="O77" t="s">
         <v>217</v>
-      </c>
-      <c r="O77" t="s">
-        <v>218</v>
       </c>
       <c r="P77" t="s">
         <v>35</v>
@@ -9463,13 +9453,13 @@
         <v>134</v>
       </c>
       <c r="C78" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D78" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E78" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F78" t="s">
         <v>29</v>
@@ -9478,28 +9468,28 @@
         <v>27</v>
       </c>
       <c r="H78" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I78" s="2">
         <v>46230</v>
       </c>
       <c r="J78" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L78" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M78" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N78" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O78" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P78" t="s">
         <v>35</v>
@@ -9513,13 +9503,13 @@
         <v>134</v>
       </c>
       <c r="C79" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D79" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F79" t="s">
         <v>29</v>
@@ -9528,28 +9518,28 @@
         <v>27</v>
       </c>
       <c r="H79" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I79" s="2">
         <v>46230</v>
       </c>
       <c r="J79" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="L79" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="M79" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N79" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O79" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P79" t="s">
         <v>35</v>
@@ -9563,40 +9553,40 @@
         <v>91</v>
       </c>
       <c r="C80" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D80" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E80" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F80" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G80" t="s">
         <v>27</v>
       </c>
       <c r="H80" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I80" s="2">
         <v>46226</v>
       </c>
       <c r="J80" t="s">
+        <v>252</v>
+      </c>
+      <c r="K80" t="s">
+        <v>79</v>
+      </c>
+      <c r="L80" t="s">
+        <v>79</v>
+      </c>
+      <c r="M80" t="s">
         <v>253</v>
       </c>
-      <c r="K80" t="s">
-        <v>79</v>
-      </c>
-      <c r="L80" t="s">
-        <v>79</v>
-      </c>
-      <c r="M80" t="s">
-        <v>254</v>
-      </c>
       <c r="N80" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O80" t="s">
         <v>127</v>
@@ -9613,40 +9603,40 @@
         <v>91</v>
       </c>
       <c r="C81" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D81" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E81" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F81" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G81" t="s">
         <v>27</v>
       </c>
       <c r="H81" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I81" s="2">
         <v>46241</v>
       </c>
       <c r="J81" t="s">
+        <v>252</v>
+      </c>
+      <c r="K81" t="s">
+        <v>79</v>
+      </c>
+      <c r="L81" t="s">
+        <v>79</v>
+      </c>
+      <c r="M81" t="s">
         <v>253</v>
       </c>
-      <c r="K81" t="s">
-        <v>79</v>
-      </c>
-      <c r="L81" t="s">
-        <v>79</v>
-      </c>
-      <c r="M81" t="s">
-        <v>254</v>
-      </c>
       <c r="N81" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O81" t="s">
         <v>127</v>
@@ -9663,40 +9653,40 @@
         <v>91</v>
       </c>
       <c r="C82" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D82" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E82" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F82" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G82" t="s">
         <v>27</v>
       </c>
       <c r="H82" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I82" s="2">
         <v>46235</v>
       </c>
       <c r="J82" t="s">
+        <v>252</v>
+      </c>
+      <c r="K82" t="s">
+        <v>79</v>
+      </c>
+      <c r="L82" t="s">
+        <v>79</v>
+      </c>
+      <c r="M82" t="s">
         <v>253</v>
       </c>
-      <c r="K82" t="s">
-        <v>79</v>
-      </c>
-      <c r="L82" t="s">
-        <v>79</v>
-      </c>
-      <c r="M82" t="s">
-        <v>254</v>
-      </c>
       <c r="N82" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O82" t="s">
         <v>127</v>
@@ -9713,40 +9703,40 @@
         <v>91</v>
       </c>
       <c r="C83" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D83" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E83" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F83" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G83" t="s">
         <v>27</v>
       </c>
       <c r="H83" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I83" s="2">
         <v>46239</v>
       </c>
       <c r="J83" t="s">
+        <v>252</v>
+      </c>
+      <c r="K83" t="s">
+        <v>79</v>
+      </c>
+      <c r="L83" t="s">
+        <v>79</v>
+      </c>
+      <c r="M83" t="s">
         <v>253</v>
       </c>
-      <c r="K83" t="s">
-        <v>79</v>
-      </c>
-      <c r="L83" t="s">
-        <v>79</v>
-      </c>
-      <c r="M83" t="s">
-        <v>254</v>
-      </c>
       <c r="N83" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="O83" t="s">
         <v>127</v>
@@ -9756,6 +9746,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P83" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <dataValidations count="9">
     <dataValidation type="list" sqref="B2:B82">
       <formula1>"胡晓玲,董贇晴,张萌凯,姜陆一,李娟,齐楚捷,许夏露,李晨观"</formula1>

--- a/data/数据源8.10-8.14.xlsx
+++ b/data/数据源8.10-8.14.xlsx
@@ -796,6 +796,9 @@
     <t>淘宝闪购</t>
   </si>
   <si>
+    <t>郭周洲</t>
+  </si>
+  <si>
     <t>1-3w</t>
   </si>
   <si>
@@ -1066,9 +1069,6 @@
   </si>
   <si>
     <t>三个月</t>
-  </si>
-  <si>
-    <t>郭周洲</t>
   </si>
   <si>
     <t>全职</t>
@@ -2378,7 +2378,7 @@
   <sheetFormatPr defaultColWidth="9.64285714285714" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="9.64285714285714" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="9.64285714285714" customWidth="1"/>
     <col min="9" max="13" width="19" customWidth="1"/>
     <col min="14" max="14" width="8.71428571428571" customWidth="1"/>
     <col min="15" max="15" width="10.5714285714286" customWidth="1"/>
@@ -4848,7 +4848,7 @@
         <v>163</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="E39" t="s">
         <v>29</v>
@@ -4857,7 +4857,7 @@
         <v>30</v>
       </c>
       <c r="G39" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I39" t="s">
         <v>32</v>
@@ -4896,16 +4896,16 @@
     </row>
     <row r="40" ht="25.5" customHeight="1" spans="1:22">
       <c r="A40" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C40" t="s">
         <v>163</v>
       </c>
       <c r="D40" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="E40" t="s">
         <v>29</v>
@@ -4914,7 +4914,7 @@
         <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I40" t="s">
         <v>32</v>
@@ -4953,16 +4953,16 @@
     </row>
     <row r="41" ht="25.5" customHeight="1" spans="1:22">
       <c r="A41" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C41" t="s">
         <v>163</v>
       </c>
       <c r="D41" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="E41" t="s">
         <v>46</v>
@@ -4971,7 +4971,7 @@
         <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I41" t="s">
         <v>121</v>
@@ -5010,16 +5010,16 @@
     </row>
     <row r="42" ht="25.5" customHeight="1" spans="1:22">
       <c r="A42" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C42" t="s">
         <v>163</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="E42" t="s">
         <v>46</v>
@@ -5028,7 +5028,7 @@
         <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I42" t="s">
         <v>121</v>
@@ -5067,16 +5067,16 @@
     </row>
     <row r="43" ht="25.5" customHeight="1" spans="1:22">
       <c r="A43" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C43" t="s">
         <v>163</v>
       </c>
       <c r="D43" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="E43" t="s">
         <v>29</v>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="44" ht="25.5" customHeight="1" spans="1:22">
       <c r="A44" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B44" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
@@ -5139,7 +5139,7 @@
         <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I44" t="s">
         <v>121</v>
@@ -5178,10 +5178,10 @@
     </row>
     <row r="45" ht="25.5" customHeight="1" spans="1:22">
       <c r="A45" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C45" t="s">
         <v>27</v>
@@ -5196,7 +5196,7 @@
         <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I45" t="s">
         <v>32</v>
@@ -5235,10 +5235,10 @@
     </row>
     <row r="46" ht="25.5" customHeight="1" spans="1:22">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C46" t="s">
         <v>27</v>
@@ -5253,7 +5253,7 @@
         <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I46" t="s">
         <v>32</v>
@@ -5292,10 +5292,10 @@
     </row>
     <row r="47" ht="25.5" customHeight="1" spans="1:22">
       <c r="A47" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B47" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C47" t="s">
         <v>27</v>
@@ -5313,7 +5313,7 @@
         <v>130</v>
       </c>
       <c r="I47" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J47">
         <v>0</v>
@@ -5349,7 +5349,7 @@
     </row>
     <row r="48" ht="25.5" customHeight="1" spans="1:22">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s">
         <v>125</v>
@@ -5361,7 +5361,7 @@
         <v>79</v>
       </c>
       <c r="E48" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F48" t="s">
         <v>30</v>
@@ -5409,7 +5409,7 @@
     </row>
     <row r="49" ht="25.5" customHeight="1" spans="1:20">
       <c r="A49" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B49" t="s">
         <v>129</v>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="50" ht="25.5" customHeight="1" spans="1:20">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -5520,7 +5520,7 @@
     </row>
     <row r="51" ht="25.5" customHeight="1" spans="1:20">
       <c r="A51" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -5535,7 +5535,7 @@
         <v>30</v>
       </c>
       <c r="G51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I51" t="s">
         <v>48</v>
@@ -5577,7 +5577,7 @@
     <extLst/>
   </autoFilter>
   <dataValidations count="5">
-    <dataValidation type="list" sqref="D2:D50">
+    <dataValidation type="list" sqref="D2:D39 D40:D43 D44:D50">
       <formula1>"张蓉蓉,吴双双,巢育敏,刘新风,后台"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="H2:H50">
@@ -5595,6 +5595,9 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:Y51" listDataValidation="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -5609,52 +5612,52 @@
   <sheetData>
     <row r="1" ht="13" customHeight="1" spans="1:16">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" ht="25.5" customHeight="1" spans="1:16">
@@ -5665,13 +5668,13 @@
         <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="E2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F2" t="s">
         <v>46</v>
@@ -5680,19 +5683,19 @@
         <v>163</v>
       </c>
       <c r="H2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I2" s="2">
         <v>46251</v>
       </c>
       <c r="J2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K2" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="L2" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="M2" t="s">
         <v>210</v>
@@ -5715,13 +5718,13 @@
         <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D3" t="s">
         <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F3" t="s">
         <v>29</v>
@@ -5765,13 +5768,13 @@
         <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D4" t="s">
         <v>218</v>
       </c>
       <c r="E4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F4" t="s">
         <v>46</v>
@@ -5786,7 +5789,7 @@
         <v>46160</v>
       </c>
       <c r="J4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K4" t="s">
         <v>79</v>
@@ -5815,13 +5818,13 @@
         <v>42</v>
       </c>
       <c r="C5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D5" t="s">
         <v>220</v>
       </c>
       <c r="E5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F5" t="s">
         <v>29</v>
@@ -5836,7 +5839,7 @@
         <v>46167</v>
       </c>
       <c r="J5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K5" t="s">
         <v>50</v>
@@ -5865,13 +5868,13 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D6" t="s">
         <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F6" t="s">
         <v>46</v>
@@ -5886,7 +5889,7 @@
         <v>46168</v>
       </c>
       <c r="J6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K6" t="s">
         <v>50</v>
@@ -5915,13 +5918,13 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D7" t="s">
         <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F7" t="s">
         <v>59</v>
@@ -5936,7 +5939,7 @@
         <v>46174</v>
       </c>
       <c r="J7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K7" t="s">
         <v>50</v>
@@ -5965,13 +5968,13 @@
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D8" t="s">
         <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F8" t="s">
         <v>29</v>
@@ -6015,13 +6018,13 @@
         <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D9" t="s">
         <v>226</v>
       </c>
       <c r="E9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F9" t="s">
         <v>46</v>
@@ -6036,7 +6039,7 @@
         <v>46161</v>
       </c>
       <c r="J9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K9" t="s">
         <v>79</v>
@@ -6065,13 +6068,13 @@
         <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D10" t="s">
         <v>228</v>
       </c>
       <c r="E10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F10" t="s">
         <v>46</v>
@@ -6086,7 +6089,7 @@
         <v>46161</v>
       </c>
       <c r="J10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K10" t="s">
         <v>79</v>
@@ -6115,13 +6118,13 @@
         <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D11" t="s">
         <v>229</v>
       </c>
       <c r="E11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F11" t="s">
         <v>46</v>
@@ -6136,7 +6139,7 @@
         <v>46167</v>
       </c>
       <c r="J11" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K11" t="s">
         <v>86</v>
@@ -6165,13 +6168,13 @@
         <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D12" t="s">
         <v>230</v>
       </c>
       <c r="E12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F12" t="s">
         <v>46</v>
@@ -6186,7 +6189,7 @@
         <v>46170</v>
       </c>
       <c r="J12" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K12" t="s">
         <v>79</v>
@@ -6215,13 +6218,13 @@
         <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D13" t="s">
         <v>231</v>
       </c>
       <c r="E13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F13" t="s">
         <v>46</v>
@@ -6236,7 +6239,7 @@
         <v>46164</v>
       </c>
       <c r="J13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K13" t="s">
         <v>86</v>
@@ -6265,13 +6268,13 @@
         <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D14" t="s">
         <v>233</v>
       </c>
       <c r="E14" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F14" t="s">
         <v>46</v>
@@ -6286,7 +6289,7 @@
         <v>46181</v>
       </c>
       <c r="J14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K14" t="s">
         <v>50</v>
@@ -6315,13 +6318,13 @@
         <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D15" t="s">
         <v>234</v>
       </c>
       <c r="E15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F15" t="s">
         <v>46</v>
@@ -6336,7 +6339,7 @@
         <v>46174</v>
       </c>
       <c r="J15" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K15" t="s">
         <v>86</v>
@@ -6365,13 +6368,13 @@
         <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D16" t="s">
         <v>236</v>
       </c>
       <c r="E16" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F16" t="s">
         <v>46</v>
@@ -6386,7 +6389,7 @@
         <v>46174</v>
       </c>
       <c r="J16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K16" t="s">
         <v>86</v>
@@ -6415,13 +6418,13 @@
         <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D17" t="s">
         <v>237</v>
       </c>
       <c r="E17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F17" t="s">
         <v>29</v>
@@ -6436,7 +6439,7 @@
         <v>46181</v>
       </c>
       <c r="J17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K17" t="s">
         <v>50</v>
@@ -6465,13 +6468,13 @@
         <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D18" t="s">
         <v>238</v>
       </c>
       <c r="E18" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F18" t="s">
         <v>29</v>
@@ -6486,7 +6489,7 @@
         <v>46188</v>
       </c>
       <c r="J18" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K18" t="s">
         <v>50</v>
@@ -6515,13 +6518,13 @@
         <v>42</v>
       </c>
       <c r="C19" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D19" t="s">
         <v>239</v>
       </c>
       <c r="E19" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F19" t="s">
         <v>29</v>
@@ -6536,7 +6539,7 @@
         <v>46188</v>
       </c>
       <c r="J19" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K19" t="s">
         <v>50</v>
@@ -6565,13 +6568,13 @@
         <v>42</v>
       </c>
       <c r="C20" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D20" t="s">
         <v>240</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F20" t="s">
         <v>46</v>
@@ -6586,7 +6589,7 @@
         <v>46188</v>
       </c>
       <c r="J20" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K20" t="s">
         <v>50</v>
@@ -6615,13 +6618,13 @@
         <v>42</v>
       </c>
       <c r="C21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D21" t="s">
         <v>241</v>
       </c>
       <c r="E21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F21" t="s">
         <v>29</v>
@@ -6636,7 +6639,7 @@
         <v>46188</v>
       </c>
       <c r="J21" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K21" t="s">
         <v>50</v>
@@ -6665,13 +6668,13 @@
         <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D22" t="s">
         <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F22" t="s">
         <v>46</v>
@@ -6686,7 +6689,7 @@
         <v>46196</v>
       </c>
       <c r="J22" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K22" t="s">
         <v>93</v>
@@ -6715,13 +6718,13 @@
         <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D23" t="s">
         <v>243</v>
       </c>
       <c r="E23" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F23" t="s">
         <v>46</v>
@@ -6736,7 +6739,7 @@
         <v>46198</v>
       </c>
       <c r="J23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K23" t="s">
         <v>93</v>
@@ -6765,13 +6768,13 @@
         <v>91</v>
       </c>
       <c r="C24" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D24" t="s">
         <v>244</v>
       </c>
       <c r="E24" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F24" t="s">
         <v>46</v>
@@ -6786,7 +6789,7 @@
         <v>46199</v>
       </c>
       <c r="J24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K24" t="s">
         <v>93</v>
@@ -6815,13 +6818,13 @@
         <v>42</v>
       </c>
       <c r="C25" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D25" t="s">
         <v>246</v>
       </c>
       <c r="E25" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F25" t="s">
         <v>46</v>
@@ -6836,7 +6839,7 @@
         <v>46195</v>
       </c>
       <c r="J25" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K25" t="s">
         <v>50</v>
@@ -6915,7 +6918,7 @@
         <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D27" t="s">
         <v>254</v>
@@ -6936,7 +6939,7 @@
         <v>46204</v>
       </c>
       <c r="J27" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K27" t="s">
         <v>79</v>
@@ -6965,7 +6968,7 @@
         <v>91</v>
       </c>
       <c r="C28" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D28" t="s">
         <v>257</v>
@@ -6986,7 +6989,7 @@
         <v>46204</v>
       </c>
       <c r="J28" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K28" t="s">
         <v>79</v>
@@ -7265,7 +7268,7 @@
         <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D34" t="s">
         <v>266</v>
@@ -7286,13 +7289,13 @@
         <v>46209</v>
       </c>
       <c r="J34" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K34" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="L34" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="M34" t="s">
         <v>210</v>
@@ -7315,13 +7318,13 @@
         <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D35" t="s">
         <v>268</v>
       </c>
       <c r="E35" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F35" t="s">
         <v>46</v>
@@ -7336,7 +7339,7 @@
         <v>46204</v>
       </c>
       <c r="J35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K35" t="s">
         <v>93</v>
@@ -7415,13 +7418,13 @@
         <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D37" t="s">
         <v>270</v>
       </c>
       <c r="E37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F37" t="s">
         <v>46</v>
@@ -7436,7 +7439,7 @@
         <v>46209</v>
       </c>
       <c r="J37" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K37" t="s">
         <v>93</v>
@@ -7465,13 +7468,13 @@
         <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D38" t="s">
         <v>272</v>
       </c>
       <c r="E38" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F38" t="s">
         <v>46</v>
@@ -7486,7 +7489,7 @@
         <v>46224</v>
       </c>
       <c r="J38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K38" t="s">
         <v>79</v>
@@ -7515,7 +7518,7 @@
         <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D39" t="s">
         <v>273</v>
@@ -7536,7 +7539,7 @@
         <v>46209</v>
       </c>
       <c r="J39" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K39" t="s">
         <v>79</v>
@@ -7565,7 +7568,7 @@
         <v>42</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D40" t="s">
         <v>274</v>
@@ -7586,7 +7589,7 @@
         <v>46209</v>
       </c>
       <c r="J40" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K40" t="s">
         <v>79</v>
@@ -7615,7 +7618,7 @@
         <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D41" t="s">
         <v>275</v>
@@ -7636,7 +7639,7 @@
         <v>46209</v>
       </c>
       <c r="J41" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K41" t="s">
         <v>79</v>
@@ -7665,13 +7668,13 @@
         <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D42" t="s">
         <v>276</v>
       </c>
       <c r="E42" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F42" t="s">
         <v>46</v>
@@ -7686,7 +7689,7 @@
         <v>46210</v>
       </c>
       <c r="J42" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K42" t="s">
         <v>93</v>
@@ -7715,13 +7718,13 @@
         <v>122</v>
       </c>
       <c r="C43" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
         <v>277</v>
       </c>
       <c r="E43" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F43" t="s">
         <v>46</v>
@@ -7736,7 +7739,7 @@
         <v>46209</v>
       </c>
       <c r="J43" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K43" t="s">
         <v>93</v>
@@ -7815,7 +7818,7 @@
         <v>134</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D45" t="s">
         <v>281</v>
@@ -7836,7 +7839,7 @@
         <v>46210</v>
       </c>
       <c r="J45" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K45" t="s">
         <v>86</v>
@@ -7865,7 +7868,7 @@
         <v>134</v>
       </c>
       <c r="C46" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D46" t="s">
         <v>283</v>
@@ -7886,7 +7889,7 @@
         <v>46210</v>
       </c>
       <c r="J46" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K46" t="s">
         <v>86</v>
@@ -7915,7 +7918,7 @@
         <v>134</v>
       </c>
       <c r="C47" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D47" t="s">
         <v>284</v>
@@ -7936,7 +7939,7 @@
         <v>46210</v>
       </c>
       <c r="J47" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K47" t="s">
         <v>86</v>
@@ -7965,7 +7968,7 @@
         <v>134</v>
       </c>
       <c r="C48" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D48" t="s">
         <v>285</v>
@@ -7986,7 +7989,7 @@
         <v>46210</v>
       </c>
       <c r="J48" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K48" t="s">
         <v>86</v>
@@ -8259,13 +8262,13 @@
         <v>122</v>
       </c>
       <c r="C54" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D54" t="s">
         <v>291</v>
       </c>
       <c r="E54" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F54" t="s">
         <v>46</v>
@@ -8280,7 +8283,7 @@
         <v>46217</v>
       </c>
       <c r="J54" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K54" t="s">
         <v>93</v>
@@ -8309,13 +8312,13 @@
         <v>122</v>
       </c>
       <c r="C55" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D55" t="s">
         <v>292</v>
       </c>
       <c r="E55" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F55" t="s">
         <v>46</v>
@@ -8330,7 +8333,7 @@
         <v>46223</v>
       </c>
       <c r="J55" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K55" t="s">
         <v>93</v>
@@ -8359,13 +8362,13 @@
         <v>122</v>
       </c>
       <c r="C56" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D56" t="s">
         <v>293</v>
       </c>
       <c r="E56" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F56" t="s">
         <v>46</v>
@@ -8380,7 +8383,7 @@
         <v>46217</v>
       </c>
       <c r="J56" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K56" t="s">
         <v>93</v>
@@ -8409,13 +8412,13 @@
         <v>122</v>
       </c>
       <c r="C57" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D57" t="s">
         <v>294</v>
       </c>
       <c r="E57" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F57" t="s">
         <v>46</v>
@@ -8430,7 +8433,7 @@
         <v>46217</v>
       </c>
       <c r="J57" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K57" t="s">
         <v>93</v>
@@ -8459,13 +8462,13 @@
         <v>122</v>
       </c>
       <c r="C58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D58" t="s">
         <v>295</v>
       </c>
       <c r="E58" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F58" t="s">
         <v>46</v>
@@ -8509,7 +8512,7 @@
         <v>134</v>
       </c>
       <c r="C59" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D59" t="s">
         <v>298</v>
@@ -8530,7 +8533,7 @@
         <v>46216</v>
       </c>
       <c r="J59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K59" t="s">
         <v>224</v>
@@ -8707,13 +8710,13 @@
         <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D63" t="s">
         <v>304</v>
       </c>
       <c r="E63" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F63" t="s">
         <v>46</v>
@@ -8728,7 +8731,7 @@
         <v>46223</v>
       </c>
       <c r="J63" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K63" t="s">
         <v>93</v>
@@ -8757,13 +8760,13 @@
         <v>122</v>
       </c>
       <c r="C64" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D64" t="s">
         <v>305</v>
       </c>
       <c r="E64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F64" t="s">
         <v>46</v>
@@ -8778,7 +8781,7 @@
         <v>46224</v>
       </c>
       <c r="J64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K64" t="s">
         <v>93</v>
@@ -8878,7 +8881,7 @@
         <v>46220</v>
       </c>
       <c r="J66" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K66" t="s">
         <v>79</v>
@@ -8928,7 +8931,7 @@
         <v>46220</v>
       </c>
       <c r="J67" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K67" t="s">
         <v>79</v>
@@ -8978,7 +8981,7 @@
         <v>46220</v>
       </c>
       <c r="J68" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K68" t="s">
         <v>79</v>
@@ -9157,7 +9160,7 @@
         <v>134</v>
       </c>
       <c r="C72" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D72" t="s">
         <v>316</v>
@@ -9178,7 +9181,7 @@
         <v>46224</v>
       </c>
       <c r="J72" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K72" t="s">
         <v>86</v>
@@ -9207,7 +9210,7 @@
         <v>134</v>
       </c>
       <c r="C73" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D73" t="s">
         <v>317</v>
@@ -9228,7 +9231,7 @@
         <v>46224</v>
       </c>
       <c r="J73" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K73" t="s">
         <v>86</v>
@@ -9403,13 +9406,13 @@
         <v>122</v>
       </c>
       <c r="C77" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D77" t="s">
         <v>321</v>
       </c>
       <c r="E77" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F77" t="s">
         <v>46</v>
@@ -9424,7 +9427,7 @@
         <v>46232</v>
       </c>
       <c r="J77" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K77" t="s">
         <v>86</v>
@@ -9453,7 +9456,7 @@
         <v>134</v>
       </c>
       <c r="C78" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D78" t="s">
         <v>322</v>
@@ -9474,7 +9477,7 @@
         <v>46230</v>
       </c>
       <c r="J78" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K78" t="s">
         <v>224</v>
@@ -9503,7 +9506,7 @@
         <v>134</v>
       </c>
       <c r="C79" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D79" t="s">
         <v>323</v>
@@ -9524,7 +9527,7 @@
         <v>46230</v>
       </c>
       <c r="J79" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K79" t="s">
         <v>224</v>
